--- a/data/dataset_sesiones.xlsx
+++ b/data/dataset_sesiones.xlsx
@@ -484,39 +484,39 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Potrerillos</t>
+          <t>rio de la plata</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>780</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>norte</t>
         </is>
       </c>
     </row>

--- a/data/dataset_sesiones.xlsx
+++ b/data/dataset_sesiones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,44 +481,100 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>22-08-2026</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>rio de la plata</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>Potrerillos</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>50min</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>22Knt</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5mm</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70mm</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>700mm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Potrerillos</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>40min</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>22Knt</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5mm</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>50mm</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>700mm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>norte</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/dataset_sesiones.xlsx
+++ b/data/dataset_sesiones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1004"/>
+  <dimension ref="A1:I1005"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39598,7 +39598,48 @@
           <t>700</t>
         </is>
       </c>
-      <c r="I1004" t="inlineStr">
+      <c r="I1004" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>potrerillos</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D1005" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E1005" t="n">
+        <v>93</v>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H1005" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I1005" t="inlineStr">
         <is>
           <t>6</t>
         </is>

--- a/data/dataset_sesiones.xlsx
+++ b/data/dataset_sesiones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1005"/>
+  <dimension ref="A1:I1006"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39478,7 +39478,7 @@
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>22-05-2026</t>
+          <t>22-06-2025</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
@@ -39486,35 +39486,27 @@
           <t>Potrerillos</t>
         </is>
       </c>
-      <c r="C1002" t="inlineStr">
-        <is>
-          <t>50 min</t>
-        </is>
-      </c>
-      <c r="D1002" t="inlineStr">
-        <is>
-          <t>22 Knt</t>
-        </is>
-      </c>
-      <c r="E1002" t="inlineStr">
-        <is>
-          <t>Sur</t>
-        </is>
+      <c r="C1002" t="n">
+        <v>60</v>
+      </c>
+      <c r="D1002" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E1002" t="n">
+        <v>2.1</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
-          <t>5mm</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G1002" t="inlineStr">
         <is>
-          <t>70mm</t>
-        </is>
-      </c>
-      <c r="H1002" t="inlineStr">
-        <is>
-          <t>700mm</t>
-        </is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H1002" t="n">
+        <v>700</v>
       </c>
       <c r="I1002" t="n">
         <v>6</v>
@@ -39523,7 +39515,7 @@
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>22-06-2025</t>
+          <t>22-05-20025</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
@@ -39531,20 +39523,18 @@
           <t>Potrerillos</t>
         </is>
       </c>
-      <c r="C1003" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="C1003" t="n">
+        <v>60</v>
       </c>
       <c r="D1003" t="n">
         <v>2.1</v>
       </c>
       <c r="E1003" t="n">
-        <v>2.1</v>
+        <v>93</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G1003" t="inlineStr">
@@ -39552,10 +39542,8 @@
           <t>70</t>
         </is>
       </c>
-      <c r="H1003" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
+      <c r="H1003" t="n">
+        <v>700</v>
       </c>
       <c r="I1003" t="n">
         <v>6</v>
@@ -39564,18 +39552,16 @@
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>22-05-20025</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>Potrerillos</t>
-        </is>
-      </c>
-      <c r="C1004" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+          <t>potrerillos</t>
+        </is>
+      </c>
+      <c r="C1004" t="n">
+        <v>50</v>
       </c>
       <c r="D1004" t="n">
         <v>2.1</v>
@@ -39585,18 +39571,16 @@
       </c>
       <c r="F1004" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G1004" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H1004" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H1004" t="n">
+        <v>700</v>
       </c>
       <c r="I1004" t="n">
         <v>6</v>
@@ -39605,24 +39589,24 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>potrerillos</t>
-        </is>
-      </c>
-      <c r="C1005" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+          <t>BUENOS AIRES</t>
+        </is>
+      </c>
+      <c r="C1005" t="n">
+        <v>60</v>
       </c>
       <c r="D1005" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E1005" t="n">
-        <v>93</v>
+        <v>5.5</v>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -39631,15 +39615,56 @@
       </c>
       <c r="G1005" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H1005" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="I1005" t="inlineStr">
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H1005" t="n">
+        <v>800</v>
+      </c>
+      <c r="I1005" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>mar del plata</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D1006" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="I1006" t="inlineStr">
         <is>
           <t>6</t>
         </is>

--- a/data/dataset_sesiones.xlsx
+++ b/data/dataset_sesiones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1006"/>
+  <dimension ref="A1:I1007"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39636,10 +39636,8 @@
           <t>mar del plata</t>
         </is>
       </c>
-      <c r="C1006" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="C1006" t="n">
+        <v>160</v>
       </c>
       <c r="D1006" t="n">
         <v>12.2</v>
@@ -39659,14 +39657,55 @@
           <t>100</t>
         </is>
       </c>
-      <c r="H1006" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="I1006" t="inlineStr">
-        <is>
-          <t>6</t>
+      <c r="H1006" t="n">
+        <v>800</v>
+      </c>
+      <c r="I1006" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>Potrerillos</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D1007" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>Este</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>

--- a/data/dataset_sesiones.xlsx
+++ b/data/dataset_sesiones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1007"/>
+  <dimension ref="A1:I1008"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39675,10 +39675,8 @@
           <t>Potrerillos</t>
         </is>
       </c>
-      <c r="C1007" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="C1007" t="n">
+        <v>50</v>
       </c>
       <c r="D1007" t="n">
         <v>3.3</v>
@@ -39698,14 +39696,55 @@
           <t>70</t>
         </is>
       </c>
-      <c r="H1007" t="inlineStr">
+      <c r="H1007" t="n">
+        <v>700</v>
+      </c>
+      <c r="I1007" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>Potrerillos</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D1008" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H1008" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="I1007" t="inlineStr">
-        <is>
-          <t>7</t>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>

--- a/data/dataset_sesiones.xlsx
+++ b/data/dataset_sesiones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1008"/>
+  <dimension ref="A1:I1009"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39714,10 +39714,8 @@
           <t>Potrerillos</t>
         </is>
       </c>
-      <c r="C1008" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
+      <c r="C1008" t="n">
+        <v>120</v>
       </c>
       <c r="D1008" t="n">
         <v>1.8</v>
@@ -39737,15 +39735,52 @@
           <t>70</t>
         </is>
       </c>
-      <c r="H1008" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="I1008" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="H1008" t="n">
+        <v>700</v>
+      </c>
+      <c r="I1008" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>Mar del plata</t>
+        </is>
+      </c>
+      <c r="C1009" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1009" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>Sudoeste</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="I1009" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
